--- a/analysis/data/annotation/[Archived] Labeling SDG 14_ Life below water - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 14_ Life below water - Benchmarking Dataset.xlsx
@@ -19252,7 +19252,7 @@
     <row r="2">
       <c r="A2" s="24" t="str">
         <f t="shared" ref="A2:A85" si="1">IF(NOT(ISBLANK(B2)), LEFT(MD5(B2), 7), "")</f>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>117</v>
@@ -19273,7 +19273,7 @@
     <row r="3">
       <c r="A3" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>115</v>
@@ -19294,7 +19294,7 @@
     <row r="4">
       <c r="A4" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>299</v>
@@ -19315,7 +19315,7 @@
     <row r="5">
       <c r="A5" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>239</v>
@@ -19336,7 +19336,7 @@
     <row r="6">
       <c r="A6" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>128</v>
@@ -19357,7 +19357,7 @@
     <row r="7">
       <c r="A7" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>308</v>
@@ -19378,7 +19378,7 @@
     <row r="8">
       <c r="A8" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>289</v>
@@ -19402,7 +19402,7 @@
     <row r="9">
       <c r="A9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>140</v>
@@ -19423,7 +19423,7 @@
     <row r="10">
       <c r="A10" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>163</v>
@@ -19444,7 +19444,7 @@
     <row r="11">
       <c r="A11" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>205</v>
@@ -19465,7 +19465,7 @@
     <row r="12">
       <c r="A12" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>145</v>
@@ -19486,7 +19486,7 @@
     <row r="13">
       <c r="A13" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>257</v>
@@ -19507,7 +19507,7 @@
     <row r="14">
       <c r="A14" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>167</v>
@@ -19531,7 +19531,7 @@
     <row r="15">
       <c r="A15" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>175</v>
@@ -19552,7 +19552,7 @@
     <row r="16">
       <c r="A16" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>243</v>
@@ -19576,7 +19576,7 @@
     <row r="17">
       <c r="A17" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>237</v>
@@ -19597,7 +19597,7 @@
     <row r="18">
       <c r="A18" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>247</v>
@@ -19618,7 +19618,7 @@
     <row r="19">
       <c r="A19" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>165</v>
@@ -19639,7 +19639,7 @@
     <row r="20">
       <c r="A20" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B20" s="40" t="s">
         <v>245</v>
@@ -19660,7 +19660,7 @@
     <row r="21">
       <c r="A21" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>201</v>
@@ -19681,7 +19681,7 @@
     <row r="22">
       <c r="A22" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>284</v>
@@ -19702,7 +19702,7 @@
     <row r="23">
       <c r="A23" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B23" s="40" t="s">
         <v>263</v>
@@ -19723,7 +19723,7 @@
     <row r="24">
       <c r="A24" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>302</v>
@@ -19744,7 +19744,7 @@
     <row r="25">
       <c r="A25" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>297</v>
@@ -19765,7 +19765,7 @@
     <row r="26">
       <c r="A26" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B26" s="59" t="s">
         <v>481</v>
@@ -19789,7 +19789,7 @@
     <row r="27">
       <c r="A27" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>130</v>
@@ -19810,7 +19810,7 @@
     <row r="28">
       <c r="A28" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B28" s="59" t="s">
         <v>483</v>
@@ -19834,7 +19834,7 @@
     <row r="29">
       <c r="A29" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>196</v>
@@ -19855,7 +19855,7 @@
     <row r="30">
       <c r="A30" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>152</v>
@@ -19876,7 +19876,7 @@
     <row r="31">
       <c r="A31" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B31" s="40" t="s">
         <v>280</v>
@@ -19897,7 +19897,7 @@
     <row r="32">
       <c r="A32" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>295</v>
@@ -19918,7 +19918,7 @@
     <row r="33">
       <c r="A33" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B33" s="40" t="s">
         <v>249</v>
@@ -19939,7 +19939,7 @@
     <row r="34">
       <c r="A34" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>138</v>
@@ -19960,7 +19960,7 @@
     <row r="35">
       <c r="A35" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>119</v>
@@ -19981,7 +19981,7 @@
     <row r="36">
       <c r="A36" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>267</v>
@@ -20005,7 +20005,7 @@
     <row r="37">
       <c r="A37" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B37" s="59" t="s">
         <v>485</v>
@@ -20029,7 +20029,7 @@
     <row r="38">
       <c r="A38" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B38" s="59" t="s">
         <v>487</v>
@@ -20053,7 +20053,7 @@
     <row r="39">
       <c r="A39" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B39" s="59" t="s">
         <v>489</v>
@@ -20077,7 +20077,7 @@
     <row r="40">
       <c r="A40" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>225</v>
@@ -20098,7 +20098,7 @@
     <row r="41">
       <c r="A41" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>194</v>
@@ -20119,7 +20119,7 @@
     <row r="42">
       <c r="A42" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>286</v>
@@ -20143,7 +20143,7 @@
     <row r="43">
       <c r="A43" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>184</v>
@@ -20164,7 +20164,7 @@
     <row r="44">
       <c r="A44" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B44" s="40" t="s">
         <v>154</v>
@@ -20185,7 +20185,7 @@
     <row r="45">
       <c r="A45" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B45" s="59" t="s">
         <v>490</v>
@@ -20209,7 +20209,7 @@
     <row r="46">
       <c r="A46" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>306</v>
@@ -20230,7 +20230,7 @@
     <row r="47">
       <c r="A47" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>235</v>
@@ -20251,7 +20251,7 @@
     <row r="48">
       <c r="A48" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>272</v>
@@ -20272,7 +20272,7 @@
     <row r="49">
       <c r="A49" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>217</v>
@@ -20293,7 +20293,7 @@
     <row r="50">
       <c r="A50" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B50" s="40" t="s">
         <v>274</v>
@@ -20317,7 +20317,7 @@
     <row r="51">
       <c r="A51" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>265</v>
@@ -20338,7 +20338,7 @@
     <row r="52">
       <c r="A52" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>255</v>
@@ -20359,7 +20359,7 @@
     <row r="53">
       <c r="A53" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B53" s="59" t="s">
         <v>491</v>
@@ -20383,7 +20383,7 @@
     <row r="54">
       <c r="A54" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B54" s="59" t="s">
         <v>492</v>
@@ -20407,7 +20407,7 @@
     <row r="55">
       <c r="A55" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B55" s="40" t="s">
         <v>293</v>
@@ -20428,7 +20428,7 @@
     <row r="56">
       <c r="A56" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>251</v>
@@ -20449,7 +20449,7 @@
     <row r="57">
       <c r="A57" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>231</v>
@@ -20470,7 +20470,7 @@
     <row r="58">
       <c r="A58" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B58" s="59" t="s">
         <v>493</v>
@@ -20494,7 +20494,7 @@
     <row r="59">
       <c r="A59" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>304</v>
@@ -20515,7 +20515,7 @@
     <row r="60">
       <c r="A60" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>210</v>
@@ -20536,7 +20536,7 @@
     <row r="61">
       <c r="A61" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B61" s="40" t="s">
         <v>278</v>
@@ -20560,7 +20560,7 @@
     <row r="62">
       <c r="A62" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>126</v>
@@ -20581,7 +20581,7 @@
     <row r="63">
       <c r="A63" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B63" s="59" t="s">
         <v>494</v>
@@ -20605,7 +20605,7 @@
     <row r="64">
       <c r="A64" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>136</v>
@@ -20626,7 +20626,7 @@
     <row r="65">
       <c r="A65" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>219</v>
@@ -20647,7 +20647,7 @@
     <row r="66">
       <c r="A66" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B66" s="40" t="s">
         <v>212</v>
@@ -20668,7 +20668,7 @@
     <row r="67">
       <c r="A67" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B67" s="59" t="s">
         <v>495</v>
@@ -20692,7 +20692,7 @@
     <row r="68">
       <c r="A68" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>161</v>
@@ -20713,7 +20713,7 @@
     <row r="69">
       <c r="A69" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>134</v>
@@ -20734,7 +20734,7 @@
     <row r="70">
       <c r="A70" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>109</v>
@@ -20758,7 +20758,7 @@
     <row r="71">
       <c r="A71" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B71" s="40" t="s">
         <v>199</v>
@@ -20779,7 +20779,7 @@
     <row r="72">
       <c r="A72" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>253</v>
@@ -20800,7 +20800,7 @@
     <row r="73">
       <c r="A73" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>227</v>
@@ -20821,7 +20821,7 @@
     <row r="74">
       <c r="A74" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>113</v>
@@ -20842,7 +20842,7 @@
     <row r="75">
       <c r="A75" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B75" s="40" t="s">
         <v>291</v>
@@ -20863,7 +20863,7 @@
     <row r="76">
       <c r="A76" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>241</v>
@@ -20884,7 +20884,7 @@
     <row r="77">
       <c r="A77" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>121</v>
@@ -20905,7 +20905,7 @@
     <row r="78">
       <c r="A78" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B78" s="40" t="s">
         <v>93</v>
@@ -20926,7 +20926,7 @@
     <row r="79">
       <c r="A79" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>276</v>
@@ -20947,7 +20947,7 @@
     <row r="80">
       <c r="A80" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>223</v>
@@ -20968,7 +20968,7 @@
     <row r="81">
       <c r="A81" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>180</v>
@@ -20989,7 +20989,7 @@
     <row r="82">
       <c r="A82" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>102</v>
@@ -21010,7 +21010,7 @@
     <row r="83">
       <c r="A83" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B83" s="40" t="s">
         <v>111</v>
@@ -21031,7 +21031,7 @@
     <row r="84">
       <c r="A84" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>107</v>
@@ -21052,7 +21052,7 @@
     <row r="85">
       <c r="A85" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>261</v>
